--- a/public/templates/template_import_siswa.xlsx
+++ b/public/templates/template_import_siswa.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Siswa" sheetId="1" r:id="Ra4f03f1826a74884"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R4c038c8fb2e8451a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Import Siswa" sheetId="1" r:id="Racf0bdbcde8a4211"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Petunjuk" sheetId="2" r:id="R4da89157e1834a97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daftar Kelas" sheetId="3" r:id="R5f5fd345c6294019"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -297,7 +298,7 @@
     <x:col min="8" max="8" width="18.84000015258789" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="16.149999618530273" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.479999542236328" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="12.109999656677246" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="24.899999618530273" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="9.420000076293945" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="24.899999618530273" hidden="0" customWidth="1"/>
@@ -333,7 +334,7 @@
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="4" t="str">
-        <x:v>Isi data siswa mulai baris 9. Kolom A dan B hanya bantuan, data yang dibaca NUSA adalah kolom C sampai S.</x:v>
+        <x:v>Isi data siswa mulai baris 9. Data yang dibaca NUSA adalah kolom C sampai S.</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -356,7 +357,7 @@
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="4" t="str">
-        <x:v>Wajib minimal: Nama Lengkap (C) dan Jenis Kelamin (D: L/P). NIS, NISN, dan NIK akan dipakai untuk mengecek data ganda.</x:v>
+        <x:v>Kolom KLS dipakai untuk otomatis menempatkan siswa ke kelas pada tahun pelajaran aktif. Contoh: VII.A, VIII.B, IX.C.</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -400,7 +401,7 @@
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="4" t="str">
-        <x:v>Format tanggal yang aman: 2009-07-21 atau 21/07/2009. Untuk NIS/NISN/NIK, gunakan format teks agar angka nol di depan tidak hilang.</x:v>
+        <x:v>Wajib minimal: Nama Lengkap (C) dan Jenis Kelamin (D: L/P). NIS, NISN, dan NIK dipakai untuk mengecek data ganda.</x:v>
       </x:c>
       <x:c r="B5" s="4"/>
       <x:c r="C5" s="4"/>
@@ -421,6 +422,29 @@
       <x:c r="R5" s="4"/>
       <x:c r="S5" s="4"/>
     </x:row>
+    <x:row r="6" ht="18" customHeight="1">
+      <x:c r="A6" s="4" t="str">
+        <x:v>Format tanggal yang aman: 2009-07-21 atau 21/07/2009. Untuk NIS/NISN/NIK, gunakan format teks agar angka nol di depan tidak hilang.</x:v>
+      </x:c>
+      <x:c r="B6" s="4"/>
+      <x:c r="C6" s="4"/>
+      <x:c r="D6" s="4"/>
+      <x:c r="E6" s="4"/>
+      <x:c r="F6" s="4"/>
+      <x:c r="G6" s="4"/>
+      <x:c r="H6" s="4"/>
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="4"/>
+      <x:c r="K6" s="4"/>
+      <x:c r="L6" s="4"/>
+      <x:c r="M6" s="4"/>
+      <x:c r="N6" s="4"/>
+      <x:c r="O6" s="4"/>
+      <x:c r="P6" s="4"/>
+      <x:c r="Q6" s="4"/>
+      <x:c r="R6" s="4"/>
+      <x:c r="S6" s="4"/>
+    </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="7" t="str">
         <x:v>No.</x:v>
@@ -11992,7 +12016,7 @@
     <x:col min="1" max="1" width="22.209999084472656" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="10.770000457763672" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="80.08000183105469" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="27.59000015258789" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="24.899999618530273" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22.5" customHeight="1">
@@ -12003,7 +12027,7 @@
       <x:c r="C1" s="14"/>
       <x:c r="D1" s="14"/>
     </x:row>
-    <x:row r="3" ht="34.5" customHeight="1">
+    <x:row r="3" ht="31.5" customHeight="1">
       <x:c r="A3" s="7" t="str">
         <x:v>Bagian</x:v>
       </x:c>
@@ -12017,7 +12041,7 @@
         <x:v>Contoh</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="34.5" customHeight="1">
+    <x:row r="4" ht="31.5" customHeight="1">
       <x:c r="A4" s="9" t="str">
         <x:v>Nama lengkap</x:v>
       </x:c>
@@ -12031,7 +12055,7 @@
         <x:v>Ahmad Fauzan</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="34.5" customHeight="1">
+    <x:row r="5" ht="31.5" customHeight="1">
       <x:c r="A5" s="9" t="str">
         <x:v>Jenis kelamin</x:v>
       </x:c>
@@ -12045,7 +12069,7 @@
         <x:v>L</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="34.5" customHeight="1">
+    <x:row r="6" ht="31.5" customHeight="1">
       <x:c r="A6" s="9" t="str">
         <x:v>NIS</x:v>
       </x:c>
@@ -12053,13 +12077,13 @@
         <x:v>E</x:v>
       </x:c>
       <x:c r="C6" s="9" t="str">
-        <x:v>Opsional, namun sangat disarankan. Format teks.</x:v>
+        <x:v>Opsional, namun disarankan. Format teks.</x:v>
       </x:c>
       <x:c r="D6" s="9" t="str">
-        <x:v>12345</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="34.5" customHeight="1">
+        <x:v>260001</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="31.5" customHeight="1">
       <x:c r="A7" s="9" t="str">
         <x:v>NIK</x:v>
       </x:c>
@@ -12067,13 +12091,13 @@
         <x:v>F</x:v>
       </x:c>
       <x:c r="C7" s="9" t="str">
-        <x:v>Opsional. Format teks agar tidak berubah menjadi notasi angka.</x:v>
+        <x:v>Opsional. Format teks agar angka tidak berubah.</x:v>
       </x:c>
       <x:c r="D7" s="9" t="str">
         <x:v>1374xxxxxxxxxxxx</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="34.5" customHeight="1">
+    <x:row r="8" ht="31.5" customHeight="1">
       <x:c r="A8" s="9" t="str">
         <x:v>NISN</x:v>
       </x:c>
@@ -12081,13 +12105,13 @@
         <x:v>G</x:v>
       </x:c>
       <x:c r="C8" s="9" t="str">
-        <x:v>Opsional, namun sangat disarankan. Dipakai untuk mencegah data ganda.</x:v>
+        <x:v>Opsional, namun disarankan untuk mencegah data ganda.</x:v>
       </x:c>
       <x:c r="D8" s="9" t="str">
         <x:v>0123456789</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="34.5" customHeight="1">
+    <x:row r="9" ht="31.5" customHeight="1">
       <x:c r="A9" s="9" t="str">
         <x:v>Tempat lahir</x:v>
       </x:c>
@@ -12101,7 +12125,7 @@
         <x:v>Padang Panjang</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="34.5" customHeight="1">
+    <x:row r="10" ht="31.5" customHeight="1">
       <x:c r="A10" s="9" t="str">
         <x:v>Tanggal lahir</x:v>
       </x:c>
@@ -12115,7 +12139,7 @@
         <x:v>2011-08-17</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="34.5" customHeight="1">
+    <x:row r="11" ht="31.5" customHeight="1">
       <x:c r="A11" s="9" t="str">
         <x:v>Agama</x:v>
       </x:c>
@@ -12129,7 +12153,7 @@
         <x:v>Islam</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="34.5" customHeight="1">
+    <x:row r="12" ht="31.5" customHeight="1">
       <x:c r="A12" s="9" t="str">
         <x:v>KLS</x:v>
       </x:c>
@@ -12137,13 +12161,13 @@
         <x:v>K</x:v>
       </x:c>
       <x:c r="C12" s="9" t="str">
-        <x:v>Kelas saat import. Saat ini hanya dicatat untuk ringkasan; modul kelas dibuat terpisah nanti.</x:v>
+        <x:v>Isi nama kelas aktif. NUSA akan menempatkan siswa ke kelas ini saat import.</x:v>
       </x:c>
       <x:c r="D12" s="9" t="str">
         <x:v>VII.A</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="34.5" customHeight="1">
+    <x:row r="13" ht="31.5" customHeight="1">
       <x:c r="A13" s="9" t="str">
         <x:v>Status dalam keluarga</x:v>
       </x:c>
@@ -12157,7 +12181,7 @@
         <x:v>Anak Kandung</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="34.5" customHeight="1">
+    <x:row r="14" ht="31.5" customHeight="1">
       <x:c r="A14" s="9" t="str">
         <x:v>Anak ke</x:v>
       </x:c>
@@ -12171,7 +12195,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="34.5" customHeight="1">
+    <x:row r="15" ht="31.5" customHeight="1">
       <x:c r="A15" s="9" t="str">
         <x:v>Nama orang tua</x:v>
       </x:c>
@@ -12185,7 +12209,7 @@
         <x:v>Budi / Siti</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="34.5" customHeight="1">
+    <x:row r="16" ht="31.5" customHeight="1">
       <x:c r="A16" s="9" t="str">
         <x:v>Pekerjaan orang tua</x:v>
       </x:c>
@@ -12199,7 +12223,7 @@
         <x:v>Wiraswasta</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="34.5" customHeight="1">
+    <x:row r="17" ht="31.5" customHeight="1">
       <x:c r="A17" s="9" t="str">
         <x:v>Alamat</x:v>
       </x:c>
@@ -12213,7 +12237,7 @@
         <x:v>Jl. Sudirman No. 2</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="34.5" customHeight="1">
+    <x:row r="18" ht="31.5" customHeight="1">
       <x:c r="A18" s="9" t="str">
         <x:v>Sekolah asal</x:v>
       </x:c>
@@ -12225,6 +12249,202 @@
       </x:c>
       <x:c r="D18" s="9" t="str">
         <x:v>SD Negeri ...</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="31.5" customHeight="1">
+      <x:c r="A19" s="9"/>
+      <x:c r="B19" s="9"/>
+      <x:c r="C19" s="9"/>
+      <x:c r="D19" s="9"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18.170000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.940000534057617" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="7" t="str">
+        <x:v>Nama Kelas</x:v>
+      </x:c>
+      <x:c r="B1" s="7" t="str">
+        <x:v>Tingkat</x:v>
+      </x:c>
+      <x:c r="C1" s="7" t="str">
+        <x:v>Catatan</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="9" t="str">
+        <x:v>VII.A</x:v>
+      </x:c>
+      <x:c r="B2" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C2" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="9" t="str">
+        <x:v>VII.B</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="9" t="str">
+        <x:v>VII.C</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="9" t="str">
+        <x:v>VII.D</x:v>
+      </x:c>
+      <x:c r="B5" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C5" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="9" t="str">
+        <x:v>VII.E</x:v>
+      </x:c>
+      <x:c r="B6" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="9" t="str">
+        <x:v>VIII.A</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C7" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="9" t="str">
+        <x:v>VIII.B</x:v>
+      </x:c>
+      <x:c r="B8" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C8" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="9" t="str">
+        <x:v>VIII.C</x:v>
+      </x:c>
+      <x:c r="B9" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C9" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="9" t="str">
+        <x:v>VIII.D</x:v>
+      </x:c>
+      <x:c r="B10" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C10" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="9" t="str">
+        <x:v>VIII.E</x:v>
+      </x:c>
+      <x:c r="B11" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C11" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="9" t="str">
+        <x:v>IX.A</x:v>
+      </x:c>
+      <x:c r="B12" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C12" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="9" t="str">
+        <x:v>IX.B</x:v>
+      </x:c>
+      <x:c r="B13" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C13" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="9" t="str">
+        <x:v>IX.C</x:v>
+      </x:c>
+      <x:c r="B14" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C14" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="9" t="str">
+        <x:v>IX.D</x:v>
+      </x:c>
+      <x:c r="B15" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C15" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="9" t="str">
+        <x:v>IX.E</x:v>
+      </x:c>
+      <x:c r="B16" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C16" s="9" t="str">
+        <x:v>Kelas aktif 2026/2027</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
